--- a/config/excel/common.xlsx
+++ b/config/excel/common.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t xml:space="preserve"> 字段</t>
   </si>
@@ -68,16 +68,22 @@
     <t>desc</t>
   </si>
   <si>
+    <t>dailyQuestScoreRewards</t>
+  </si>
+  <si>
+    <t>item_10000001_10000,item_10000002_100,item_20000012_3,item_40000004_1</t>
+  </si>
+  <si>
+    <t>每日任务活跃进度奖</t>
+  </si>
+  <si>
     <t>END</t>
   </si>
   <si>
-    <t>dailyQuestScoreRewards</t>
-  </si>
-  <si>
-    <t>item_10000001_10000,item_10000002_100,item_20000012_3,item_40000004_1</t>
-  </si>
-  <si>
-    <t>每日任务活跃进度奖</t>
+    <t>dailyQuestScoreSum</t>
+  </si>
+  <si>
+    <t>每日任务最大活跃值</t>
   </si>
 </sst>
 </file>
@@ -105,17 +111,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -740,13 +746,13 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1285,6 +1291,7 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
+    <col min="3" max="3" width="21.25" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="41.875" customWidth="1"/>
     <col min="6" max="6" width="92.125" customWidth="1"/>
@@ -1339,32 +1346,34 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:5">
-      <c r="B5" s="2"/>
-      <c r="C5">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4">
         <v>2</v>
       </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
